--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.24.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.24.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -851,7 +851,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.24.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.24.xlsx
@@ -416,14 +416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y18"/>
+  <dimension ref="A1:Y20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="55" customWidth="1" min="8" max="8"/>
@@ -431,7 +431,7 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.24.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.24.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0024.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0024.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -605,16 +605,20 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L10: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: right to redeem â€” a question on which there is here some</t>
+          <t>L22: stray/suspicious non-ASCII glyph(s): U+4EA7 CJK UNIFIED IDEOGRAPH-4EA7 | isolated marker/symbol line :: 产</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L15: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: right to redeemâ€”a question on which there is here some</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]17</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]17</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L15: isolated marker/symbol line :: 17</t>
@@ -622,7 +626,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L27: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]17</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
@@ -649,7 +653,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>74</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -660,24 +664,24 @@
       <c r="I3" s="1" t="inlineStr"/>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L24: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L24: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L27: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L27: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
         <is>
-          <t>L23: isolated marker/symbol line :: 2</t>
+          <t>L22: stray/suspicious non-ASCII glyph(s): U+4EA7 CJK UNIFIED IDEOGRAPH-4EA7 | isolated marker/symbol line :: 产</t>
         </is>
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L43: isolated marker/symbol line :: Â°</t>
+          <t>L27: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
@@ -715,24 +719,24 @@
       <c r="I4" s="1" t="inlineStr"/>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>L26: stray/suspicious non-ASCII glyph(s): U+2122 TRADE MARK SIGN :: æµ™</t>
+          <t>L26: stray/suspicious non-ASCII glyph(s): U+6D59 CJK UNIFIED IDEOGRAPH-6D59 | isolated marker/symbol line :: 浙</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L50: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L50: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
         <is>
-          <t>L24: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L23: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L50: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L43: isolated marker/symbol line :: °</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
@@ -771,19 +775,19 @@
       <c r="J5" s="1" t="inlineStr"/>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>L82: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L82: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
         <is>
-          <t>L25: isolated marker/symbol line :: t</t>
+          <t>L24: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>L82: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L50: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr"/>
@@ -822,19 +826,19 @@
       <c r="J6" s="1" t="inlineStr"/>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>L84: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L84: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
         <is>
-          <t>L27: isolated marker/symbol line :: 0-</t>
+          <t>L25: isolated marker/symbol line :: t</t>
         </is>
       </c>
       <c r="O6" s="1" t="inlineStr">
         <is>
-          <t>L84: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L82: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P6" s="1" t="inlineStr"/>
@@ -873,19 +877,19 @@
       <c r="J7" s="1" t="inlineStr"/>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>L90: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L90: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
         <is>
-          <t>L28: isolated marker/symbol line :: 0</t>
+          <t>L26: stray/suspicious non-ASCII glyph(s): U+6D59 CJK UNIFIED IDEOGRAPH-6D59 | isolated marker/symbol line :: 浙</t>
         </is>
       </c>
       <c r="O7" s="1" t="inlineStr">
         <is>
-          <t>L86: isolated marker/symbol line :: "</t>
+          <t>L84: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr"/>
@@ -924,19 +928,19 @@
       <c r="J8" s="1" t="inlineStr"/>
       <c r="K8" s="1" t="inlineStr">
         <is>
-          <t>L103: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L103: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
         <is>
-          <t>L29: isolated marker/symbol line :: 4</t>
+          <t>L27: isolated marker/symbol line :: 0-</t>
         </is>
       </c>
       <c r="O8" s="1" t="inlineStr">
         <is>
-          <t>L88: isolated marker/symbol line :: (</t>
+          <t>L86: isolated marker/symbol line :: "</t>
         </is>
       </c>
       <c r="P8" s="1" t="inlineStr"/>
@@ -978,12 +982,12 @@
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
         <is>
-          <t>L30: isolated marker/symbol line :: 3</t>
+          <t>L28: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O9" s="1" t="inlineStr">
         <is>
-          <t>L90: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L88: isolated marker/symbol line :: (</t>
         </is>
       </c>
       <c r="P9" s="1" t="inlineStr"/>
@@ -1025,12 +1029,12 @@
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr">
         <is>
-          <t>L31: isolated marker/symbol line :: 5</t>
+          <t>L29: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O10" s="1" t="inlineStr">
         <is>
-          <t>L92: symbol-only separator/garbage line :: 0653</t>
+          <t>L90: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P10" s="1" t="inlineStr"/>
@@ -1057,7 +1061,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1072,12 +1076,12 @@
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr">
         <is>
-          <t>L32: isolated marker/symbol line :: 2</t>
+          <t>L30: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="O11" s="1" t="inlineStr">
         <is>
-          <t>L95: isolated marker/symbol line :: r$</t>
+          <t>L92: symbol-only separator/garbage line :: 0653</t>
         </is>
       </c>
       <c r="P11" s="1" t="inlineStr"/>
@@ -1099,12 +1103,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1119,12 +1123,12 @@
       <c r="M12" s="1" t="inlineStr"/>
       <c r="N12" s="1" t="inlineStr">
         <is>
-          <t>L33: isolated marker/symbol line :: 7</t>
+          <t>L31: isolated marker/symbol line :: 5</t>
         </is>
       </c>
       <c r="O12" s="1" t="inlineStr">
         <is>
-          <t>L97: isolated marker/symbol line :: 1</t>
+          <t>L95: isolated marker/symbol line :: r$</t>
         </is>
       </c>
       <c r="P12" s="1" t="inlineStr"/>
@@ -1166,12 +1170,12 @@
       <c r="M13" s="1" t="inlineStr"/>
       <c r="N13" s="1" t="inlineStr">
         <is>
-          <t>L34: isolated marker/symbol line :: 4</t>
+          <t>L32: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O13" s="1" t="inlineStr">
         <is>
-          <t>L99: isolated marker/symbol line :: 1</t>
+          <t>L97: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="P13" s="1" t="inlineStr"/>
@@ -1213,12 +1217,12 @@
       <c r="M14" s="1" t="inlineStr"/>
       <c r="N14" s="1" t="inlineStr">
         <is>
-          <t>L35: isolated marker/symbol line :: 0</t>
+          <t>L33: isolated marker/symbol line :: 7</t>
         </is>
       </c>
       <c r="O14" s="1" t="inlineStr">
         <is>
-          <t>L101: isolated marker/symbol line :: 0</t>
+          <t>L99: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="P14" s="1" t="inlineStr"/>
@@ -1260,12 +1264,12 @@
       <c r="M15" s="1" t="inlineStr"/>
       <c r="N15" s="1" t="inlineStr">
         <is>
-          <t>L36: isolated marker/symbol line :: X</t>
+          <t>L34: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O15" s="1" t="inlineStr">
         <is>
-          <t>L103: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L101: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="P15" s="1" t="inlineStr"/>
@@ -1307,12 +1311,12 @@
       <c r="M16" s="1" t="inlineStr"/>
       <c r="N16" s="1" t="inlineStr">
         <is>
-          <t>L37: isolated marker/symbol line :: 1</t>
+          <t>L35: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O16" s="1" t="inlineStr">
         <is>
-          <t>L105: isolated marker/symbol line :: B</t>
+          <t>L103: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P16" s="1" t="inlineStr"/>
@@ -1354,10 +1358,14 @@
       <c r="M17" s="1" t="inlineStr"/>
       <c r="N17" s="1" t="inlineStr">
         <is>
-          <t>L39: isolated marker/symbol line :: 8</t>
-        </is>
-      </c>
-      <c r="O17" s="1" t="inlineStr"/>
+          <t>L36: isolated marker/symbol line :: X</t>
+        </is>
+      </c>
+      <c r="O17" s="1" t="inlineStr">
+        <is>
+          <t>L105: isolated marker/symbol line :: B</t>
+        </is>
+      </c>
       <c r="P17" s="1" t="inlineStr"/>
       <c r="Q17" s="1" t="inlineStr"/>
       <c r="R17" s="1" t="inlineStr"/>
@@ -1385,7 +1393,7 @@
       <c r="M18" s="1" t="inlineStr"/>
       <c r="N18" s="1" t="inlineStr">
         <is>
-          <t>L40: isolated marker/symbol line :: B</t>
+          <t>L37: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O18" s="1" t="inlineStr"/>
@@ -1400,6 +1408,68 @@
       <c r="X18" s="1" t="inlineStr"/>
       <c r="Y18" s="1" t="inlineStr"/>
     </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr"/>
+      <c r="B19" s="1" t="inlineStr"/>
+      <c r="C19" s="1" t="inlineStr"/>
+      <c r="D19" s="1" t="inlineStr"/>
+      <c r="E19" s="1" t="inlineStr"/>
+      <c r="F19" s="1" t="inlineStr"/>
+      <c r="G19" s="1" t="inlineStr"/>
+      <c r="H19" s="1" t="inlineStr"/>
+      <c r="I19" s="1" t="inlineStr"/>
+      <c r="J19" s="1" t="inlineStr"/>
+      <c r="K19" s="1" t="inlineStr"/>
+      <c r="L19" s="1" t="inlineStr"/>
+      <c r="M19" s="1" t="inlineStr"/>
+      <c r="N19" s="1" t="inlineStr">
+        <is>
+          <t>L39: isolated marker/symbol line :: 8</t>
+        </is>
+      </c>
+      <c r="O19" s="1" t="inlineStr"/>
+      <c r="P19" s="1" t="inlineStr"/>
+      <c r="Q19" s="1" t="inlineStr"/>
+      <c r="R19" s="1" t="inlineStr"/>
+      <c r="S19" s="1" t="inlineStr"/>
+      <c r="T19" s="1" t="inlineStr"/>
+      <c r="U19" s="1" t="inlineStr"/>
+      <c r="V19" s="1" t="inlineStr"/>
+      <c r="W19" s="1" t="inlineStr"/>
+      <c r="X19" s="1" t="inlineStr"/>
+      <c r="Y19" s="1" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr"/>
+      <c r="B20" s="1" t="inlineStr"/>
+      <c r="C20" s="1" t="inlineStr"/>
+      <c r="D20" s="1" t="inlineStr"/>
+      <c r="E20" s="1" t="inlineStr"/>
+      <c r="F20" s="1" t="inlineStr"/>
+      <c r="G20" s="1" t="inlineStr"/>
+      <c r="H20" s="1" t="inlineStr"/>
+      <c r="I20" s="1" t="inlineStr"/>
+      <c r="J20" s="1" t="inlineStr"/>
+      <c r="K20" s="1" t="inlineStr"/>
+      <c r="L20" s="1" t="inlineStr"/>
+      <c r="M20" s="1" t="inlineStr"/>
+      <c r="N20" s="1" t="inlineStr">
+        <is>
+          <t>L40: isolated marker/symbol line :: B</t>
+        </is>
+      </c>
+      <c r="O20" s="1" t="inlineStr"/>
+      <c r="P20" s="1" t="inlineStr"/>
+      <c r="Q20" s="1" t="inlineStr"/>
+      <c r="R20" s="1" t="inlineStr"/>
+      <c r="S20" s="1" t="inlineStr"/>
+      <c r="T20" s="1" t="inlineStr"/>
+      <c r="U20" s="1" t="inlineStr"/>
+      <c r="V20" s="1" t="inlineStr"/>
+      <c r="W20" s="1" t="inlineStr"/>
+      <c r="X20" s="1" t="inlineStr"/>
+      <c r="Y20" s="1" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
